--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487426_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487426_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5983</v>
+        <v>3.0781</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2443</v>
+        <v>0.9332</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8426</v>
+        <v>2.1449</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9714</v>
+        <v>0.7212</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6533</v>
+        <v>0.6704</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6819</v>
+        <v>0.0508</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4497</v>
+        <v>0.1629</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3752</v>
+        <v>0.1225</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.9255</v>
+        <v>0.0404</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5217</v>
+        <v>0.5583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2781</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2436</v>
+        <v>0.0104</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9377</v>
+        <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9794</v>
+        <v>-0.3885</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3209</v>
+        <v>0.2576</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3415</v>
+        <v>-0.6461</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3318</v>
+        <v>2.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.0564</v>
+        <v>1.492</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2754</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0036</v>
+        <v>3.017</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0191</v>
+        <v>1.6655</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9845</v>
+        <v>1.3515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7212</v>
+        <v>2.2488</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6704</v>
+        <v>1.3849</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0508</v>
+        <v>0.8639</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1629</v>
+        <v>1.6166</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1225</v>
+        <v>1.0412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0404</v>
+        <v>0.5755</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5583</v>
+        <v>0.6322</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0104</v>
+        <v>0.2885</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.463</v>
+        <v>-0.8781</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3435</v>
+        <v>-0.2264</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8064</v>
+        <v>-0.6516</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1578</v>
+        <v>0.2754</v>
       </c>
       <c r="W3" t="n">
-        <v>1.492</v>
+        <v>0.2754</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4414</v>
+        <v>2.4929</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1968</v>
+        <v>-0.8418</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2446</v>
+        <v>3.3347</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2488</v>
+        <v>2.9714</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3849</v>
+        <v>3.6533</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8639</v>
+        <v>-0.6819</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6166</v>
+        <v>1.4497</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0412</v>
+        <v>3.3752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5755</v>
+        <v>-1.9255</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6322</v>
+        <v>1.5217</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3437</v>
+        <v>0.2781</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2885</v>
+        <v>1.2436</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4538</v>
+        <v>-0.126</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6952</v>
+        <v>0.7234</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.8494</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2754</v>
+        <v>-1.3318</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2754</v>
+        <v>-1.0564</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2646</v>
+        <v>0.4204</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1817</v>
+        <v>-0.0793</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4463</v>
+        <v>0.4997</v>
       </c>
       <c r="G5" t="n">
         <v>-0.081</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3802</v>
+        <v>-0.2244</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0306</v>
+        <v>0.0717</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3496</v>
+        <v>-0.2961</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0576</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5188</v>
+        <v>-0.6698</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1226</v>
+        <v>-1.3537</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6038</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4729</v>
@@ -922,13 +922,13 @@
         <v>2.546</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5758</v>
+        <v>-0.7268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5087</v>
+        <v>0.2776</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0846</v>
+        <v>-1.0044</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0576</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6851</v>
+        <v>-1.0071</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3137</v>
+        <v>-1.7426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6286</v>
+        <v>0.7355</v>
       </c>
       <c r="G7" t="n">
         <v>1.2012</v>
@@ -1000,13 +1000,13 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1985</v>
+        <v>-0.5205</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.594</v>
+        <v>-0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6045</v>
+        <v>-0.4976</v>
       </c>
       <c r="V7" t="n">
         <v>-1.492</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8217</v>
+        <v>-2.7089</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.699</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1227</v>
+        <v>-2.0693</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2705</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4925</v>
+        <v>-0.3796</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2794</v>
+        <v>-0.22</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V8" t="n">
         <v>0.3329</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9237</v>
+        <v>-3.8897</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0656</v>
+        <v>-4.8444</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1419</v>
+        <v>0.9548</v>
       </c>
       <c r="G9" t="n">
         <v>-5.1129</v>
@@ -1156,13 +1156,13 @@
         <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.457</v>
+        <v>-0.423</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0335</v>
+        <v>0.2547</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4906</v>
+        <v>-0.6777</v>
       </c>
       <c r="V9" t="n">
         <v>0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0426</v>
+        <v>-4.4857</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5356</v>
+        <v>-4.1925</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.507</v>
+        <v>-0.2931</v>
       </c>
       <c r="G10" t="n">
         <v>-2.938</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.112</v>
+        <v>-0.3311</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9775</v>
+        <v>0.3205</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8655</v>
+        <v>-0.6516</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.885</v>
+        <v>-4.9254</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3543</v>
+        <v>-2.3145</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5307</v>
+        <v>-2.6109</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3294</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9461</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1528</v>
+        <v>-0.1129</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7933</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4344</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.569000000000001</v>
+        <v>-8.678199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.3009</v>
+        <v>-13.4097</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7319</v>
+        <v>4.7318</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0621</v>
@@ -1372,7 +1372,7 @@
         <v>-4.2231</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4587999999999999</v>
+        <v>-0.4587999999999995</v>
       </c>
       <c r="N12" t="n">
         <v>-2.6873</v>
@@ -1390,16 +1390,16 @@
         <v>17.6262</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.875499999999999</v>
+        <v>-4.9844</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4321000000000002</v>
+        <v>1.3233</v>
       </c>
       <c r="U12" t="n">
         <v>-6.307700000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.5485</v>
+        <v>-2.548500000000001</v>
       </c>
       <c r="W12" t="n">
         <v>3.5798</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.4858</v>
+        <v>7.7411</v>
       </c>
       <c r="E13" t="n">
-        <v>3.849</v>
+        <v>3.6443</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6368</v>
+        <v>4.0968</v>
       </c>
       <c r="G13" t="n">
         <v>5.4798</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5935</v>
+        <v>0.8488</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6516</v>
+        <v>0.447</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0582</v>
+        <v>0.4018</v>
       </c>
       <c r="V13" t="n">
         <v>1.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0905</v>
+        <v>6.2068</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0582</v>
+        <v>0.5699</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0322</v>
+        <v>5.6369</v>
       </c>
       <c r="G14" t="n">
         <v>3.7653</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.8124</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3694</v>
+        <v>0.1423</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0654</v>
+        <v>0.67</v>
       </c>
       <c r="V14" t="n">
         <v>1.8249</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4483</v>
+        <v>2.1993</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7766</v>
+        <v>1.3673</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6716</v>
+        <v>0.832</v>
       </c>
       <c r="G15" t="n">
         <v>1.4874</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9609</v>
+        <v>0.7119</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2039</v>
+        <v>0.7946</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.243</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.965</v>
+        <v>1.7741</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2412</v>
+        <v>-0.7529</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2062</v>
+        <v>2.527</v>
       </c>
       <c r="G16" t="n">
         <v>2.6799</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5397</v>
+        <v>0.3488</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9487</v>
+        <v>0.437</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.409</v>
+        <v>-0.0882</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2754</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0904</v>
+        <v>1.154</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6413</v>
+        <v>-3.6012</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5508999999999999</v>
+        <v>4.7552</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1939</v>
+        <v>-1.8569</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9058</v>
+        <v>1.1549</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2881</v>
+        <v>-3.0119</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2873</v>
+        <v>-4.4588</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3181</v>
+        <v>0.1956</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0308</v>
+        <v>-4.6544</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4812</v>
+        <v>2.6018</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2239</v>
+        <v>0.9593</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2573</v>
+        <v>1.6426</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.1958</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.7626</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.3756</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.3756</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-1.1751</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.1751</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.9513</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2537</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.3024</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.3329</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.0576</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8396</v>
+        <v>0.3449</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8058</v>
+        <v>0.0469</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6455</v>
+        <v>0.298</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8569</v>
+        <v>-0.115</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1549</v>
+        <v>-0.3879</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.0119</v>
+        <v>0.2729</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.4588</v>
+        <v>0.0204</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1956</v>
+        <v>0.0204</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.6544</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6018</v>
+        <v>-0.1354</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9593</v>
+        <v>-0.4083</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6426</v>
+        <v>0.2729</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5168</v>
+        <v>0.2641</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2358</v>
+        <v>0.0265</v>
       </c>
       <c r="U18" t="n">
-        <v>0.281</v>
+        <v>0.2376</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3756</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3756</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3541</v>
+        <v>0.3298</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1578</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5119</v>
+        <v>-0.3905</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.115</v>
+        <v>-1.1939</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3879</v>
+        <v>-0.9058</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2729</v>
+        <v>-0.2881</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0204</v>
+        <v>0.2873</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0204</v>
+        <v>0.3181</v>
       </c>
       <c r="L19" t="n">
+        <v>-0.0308</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.4812</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1.2239</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.2573</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.4083</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.2729</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.1958</v>
-      </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2732</v>
+        <v>1.1907</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1782</v>
+        <v>1.3327</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4515</v>
+        <v>-0.142</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.534</v>
+        <v>-1.6141</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-1.8873</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9609</v>
+        <v>0.2732</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4142</v>
+        <v>-2.7307</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7931</v>
+        <v>-1.3818</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2073</v>
+        <v>-1.3489</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7517</v>
+        <v>-1.8765</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4287</v>
+        <v>-0.6381</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3229</v>
+        <v>-1.2384</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3375</v>
+        <v>-0.8542</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2218</v>
+        <v>-0.7437</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1157</v>
+        <v>-0.1105</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1336</v>
+        <v>-2.1543</v>
       </c>
       <c r="R20" t="n">
         <v>1.7626</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2016</v>
+        <v>0.8424</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1911</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0105</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3756</v>
+        <v>0.6659</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3756</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5729</v>
+        <v>-1.8416</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9441</v>
+        <v>0.1433</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3712</v>
+        <v>-1.9848</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.291</v>
+        <v>1.4142</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0185</v>
+        <v>-0.7931</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2725</v>
+        <v>2.2073</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3356</v>
+        <v>2.7517</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0924</v>
+        <v>0.4287</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2432</v>
+        <v>2.3229</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0446</v>
+        <v>-1.3375</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07389999999999999</v>
+        <v>-1.2218</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9707</v>
+        <v>-0.1157</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5875</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5222</v>
+        <v>0.4908</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7993</v>
+        <v>0.5252</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2771</v>
+        <v>-0.0344</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2166</v>
+        <v>-2.3756</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7673</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5812</v>
+        <v>-2.4245</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5013</v>
+        <v>-3.1488</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0799</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7307</v>
+        <v>-1.291</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3818</v>
+        <v>-1.0185</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3489</v>
+        <v>-0.2725</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8765</v>
+        <v>-2.3356</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6381</v>
+        <v>-1.0924</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2384</v>
+        <v>-1.2432</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8542</v>
+        <v>1.0446</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7437</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1105</v>
+        <v>0.9707</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1247</v>
+        <v>0.6706</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3129</v>
+        <v>0.5946</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4376</v>
+        <v>0.076</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6659</v>
+        <v>-1.2166</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0.5507</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5507</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0163</v>
+        <v>-2.9361</v>
       </c>
       <c r="E23" t="n">
         <v>-1.8334</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1829</v>
+        <v>-1.1027</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5769</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1482</v>
+        <v>0.2283</v>
       </c>
       <c r="T23" t="n">
         <v>0.6405</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4923</v>
+        <v>-0.4121</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.569299999999998</v>
+        <v>10.9337</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.731600000000001</v>
+        <v>-4.731599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3008</v>
+        <v>15.6654</v>
       </c>
       <c r="G24" t="n">
         <v>5.062200000000001</v>
@@ -2296,25 +2296,25 @@
         <v>3.0674</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9947</v>
+        <v>1.994700000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4589000000000003</v>
+        <v>0.4589000000000012</v>
       </c>
       <c r="K24" t="n">
-        <v>2.687199999999999</v>
+        <v>2.6872</v>
       </c>
       <c r="L24" t="n">
         <v>-2.2284</v>
       </c>
       <c r="M24" t="n">
-        <v>4.603200000000001</v>
+        <v>4.6032</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3799999999999993</v>
+        <v>0.3799999999999994</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2232</v>
+        <v>4.223200000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-3.9168</v>
@@ -2326,19 +2326,19 @@
         <v>13.7091</v>
       </c>
       <c r="S24" t="n">
-        <v>5.8756</v>
+        <v>7.24</v>
       </c>
       <c r="T24" t="n">
-        <v>6.3077</v>
+        <v>6.307799999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4322000000000001</v>
+        <v>0.9323</v>
       </c>
       <c r="V24" t="n">
         <v>2.5483</v>
       </c>
       <c r="W24" t="n">
-        <v>6.127999999999999</v>
+        <v>6.128</v>
       </c>
       <c r="X24" t="n">
         <v>-3.5796</v>
